--- a/docs/ref/Placa Base/PB_VERIFICACIONES.xlsx
+++ b/docs/ref/Placa Base/PB_VERIFICACIONES.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.10.0.30\Civil\03 - STD TEKLA\ref\Placa Base\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\03 - STD TEKLA\repo\docs\ref\Placa Base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21D5DE00-D63E-450A-82E6-E4A747962B9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53471ACB-DD2C-4219-B774-A518D8F979C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PB" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="52">
   <si>
     <t>Perfil</t>
   </si>
@@ -183,6 +183,12 @@
   </si>
   <si>
     <t>400x350</t>
+  </si>
+  <si>
+    <t>280x280</t>
+  </si>
+  <si>
+    <t>3/4''</t>
   </si>
 </sst>
 </file>
@@ -998,8 +1004,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E8367052-7810-4CA1-9C70-F48FA2998CC0}" name="Table1" displayName="Table1" ref="A1:P30" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
-  <autoFilter ref="A1:P30" xr:uid="{E8367052-7810-4CA1-9C70-F48FA2998CC0}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E8367052-7810-4CA1-9C70-F48FA2998CC0}" name="Table1" displayName="Table1" ref="A1:P29" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
+  <autoFilter ref="A1:P29" xr:uid="{E8367052-7810-4CA1-9C70-F48FA2998CC0}"/>
   <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{F50DDB28-7D44-48CC-B5E4-97688A435C4B}" name="Perfil" dataDxfId="14"/>
     <tableColumn id="2" xr3:uid="{35C5EE2C-AEE7-4B69-9BF3-B2D0A827EA20}" name="Variante" dataDxfId="13"/>
@@ -1309,25 +1315,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:P29"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.7109375" customWidth="1"/>
+    <col min="1" max="1" width="11.6640625" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="8.28515625" customWidth="1"/>
-    <col min="4" max="4" width="13.5703125" customWidth="1"/>
-    <col min="5" max="5" width="11.5703125" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" customWidth="1"/>
-    <col min="7" max="7" width="12.42578125" customWidth="1"/>
-    <col min="8" max="8" width="25.42578125" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" customWidth="1"/>
-    <col min="10" max="12" width="14.85546875" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-    <col min="14" max="14" width="17.42578125" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" customWidth="1"/>
+    <col min="3" max="3" width="8.33203125" customWidth="1"/>
+    <col min="4" max="4" width="13.5546875" customWidth="1"/>
+    <col min="5" max="5" width="11.5546875" customWidth="1"/>
+    <col min="6" max="6" width="14.6640625" customWidth="1"/>
+    <col min="7" max="7" width="12.44140625" customWidth="1"/>
+    <col min="8" max="8" width="25.44140625" customWidth="1"/>
+    <col min="9" max="9" width="14.33203125" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="14.88671875" hidden="1" customWidth="1"/>
+    <col min="11" max="12" width="14.88671875" customWidth="1"/>
+    <col min="13" max="13" width="18.6640625" customWidth="1"/>
+    <col min="14" max="14" width="17.44140625" customWidth="1"/>
+    <col min="15" max="15" width="21.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" ht="32.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1377,7 +1384,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>11</v>
       </c>
@@ -1397,7 +1404,7 @@
         <v>19.100000000000001</v>
       </c>
       <c r="G2" s="2">
-        <f t="shared" ref="G2:G11" si="0">+ROUNDUP(3/4*25.4*IF(B2="Articulada",12,18),-1)</f>
+        <f>+ROUNDUP(3/4*25.4*IF(B2="Articulada",12,18),-1)</f>
         <v>230</v>
       </c>
       <c r="H2" s="2">
@@ -1422,14 +1429,14 @@
         <v>17</v>
       </c>
       <c r="O2" t="str">
-        <f t="shared" ref="O2:O30" si="1">+_xlfn.CONCAT(A2,"-",IF(B2="ARTICULADA","ART","EMP"),"-",C2)</f>
+        <f>+_xlfn.CONCAT(A2,"-",IF(B2="ARTICULADA","ART","EMP"),"-",C2)</f>
         <v>W6x15-ART-1°</v>
       </c>
       <c r="P2" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
@@ -1449,7 +1456,7 @@
         <v>19.100000000000001</v>
       </c>
       <c r="G3" s="2">
-        <f t="shared" si="0"/>
+        <f>+ROUNDUP(3/4*25.4*IF(B3="Articulada",12,18),-1)</f>
         <v>350</v>
       </c>
       <c r="H3" s="2">
@@ -1474,14 +1481,14 @@
         <v>17</v>
       </c>
       <c r="O3" t="str">
-        <f t="shared" si="1"/>
+        <f>+_xlfn.CONCAT(A3,"-",IF(B3="ARTICULADA","ART","EMP"),"-",C3)</f>
         <v>W6x15-EMP-1°</v>
       </c>
       <c r="P3" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>11</v>
       </c>
@@ -1501,7 +1508,7 @@
         <v>19.100000000000001</v>
       </c>
       <c r="G4" s="2">
-        <f t="shared" si="0"/>
+        <f>+ROUNDUP(3/4*25.4*IF(B4="Articulada",12,18),-1)</f>
         <v>350</v>
       </c>
       <c r="H4" s="2">
@@ -1526,14 +1533,14 @@
         <v>19</v>
       </c>
       <c r="O4" t="str">
-        <f t="shared" si="1"/>
+        <f>+_xlfn.CONCAT(A4,"-",IF(B4="ARTICULADA","ART","EMP"),"-",C4)</f>
         <v>W6x15-EMP-2°</v>
       </c>
       <c r="P4" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>23</v>
       </c>
@@ -1553,7 +1560,7 @@
         <v>19.100000000000001</v>
       </c>
       <c r="G5" s="2">
-        <f t="shared" si="0"/>
+        <f>+ROUNDUP(3/4*25.4*IF(B5="Articulada",12,18),-1)</f>
         <v>230</v>
       </c>
       <c r="H5" s="2">
@@ -1578,14 +1585,14 @@
         <v>17</v>
       </c>
       <c r="O5" t="str">
-        <f t="shared" si="1"/>
+        <f>+_xlfn.CONCAT(A5,"-",IF(B5="ARTICULADA","ART","EMP"),"-",C5)</f>
         <v>W8x18-ART-1°</v>
       </c>
       <c r="P5" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>23</v>
       </c>
@@ -1605,7 +1612,7 @@
         <v>19.100000000000001</v>
       </c>
       <c r="G6" s="2">
-        <f t="shared" si="0"/>
+        <f>+ROUNDUP(3/4*25.4*IF(B6="Articulada",12,18),-1)</f>
         <v>350</v>
       </c>
       <c r="H6" s="2">
@@ -1630,14 +1637,14 @@
         <v>17</v>
       </c>
       <c r="O6" t="str">
-        <f t="shared" si="1"/>
+        <f>+_xlfn.CONCAT(A6,"-",IF(B6="ARTICULADA","ART","EMP"),"-",C6)</f>
         <v>W8x18-EMP-1°</v>
       </c>
       <c r="P6" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>23</v>
       </c>
@@ -1657,7 +1664,7 @@
         <v>19.100000000000001</v>
       </c>
       <c r="G7" s="2">
-        <f t="shared" si="0"/>
+        <f>+ROUNDUP(3/4*25.4*IF(B7="Articulada",12,18),-1)</f>
         <v>350</v>
       </c>
       <c r="H7" s="2">
@@ -1682,14 +1689,14 @@
         <v>19</v>
       </c>
       <c r="O7" t="str">
-        <f t="shared" si="1"/>
+        <f>+_xlfn.CONCAT(A7,"-",IF(B7="ARTICULADA","ART","EMP"),"-",C7)</f>
         <v>W8x18-EMP-2°</v>
       </c>
       <c r="P7" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>26</v>
       </c>
@@ -1709,7 +1716,7 @@
         <v>19.100000000000001</v>
       </c>
       <c r="G8" s="2">
-        <f t="shared" si="0"/>
+        <f>+ROUNDUP(3/4*25.4*IF(B8="Articulada",12,18),-1)</f>
         <v>230</v>
       </c>
       <c r="H8" s="2">
@@ -1734,14 +1741,14 @@
         <v>17</v>
       </c>
       <c r="O8" t="str">
-        <f t="shared" si="1"/>
+        <f>+_xlfn.CONCAT(A8,"-",IF(B8="ARTICULADA","ART","EMP"),"-",C8)</f>
         <v>W8x31-ART-1°</v>
       </c>
       <c r="P8" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>26</v>
       </c>
@@ -1761,7 +1768,7 @@
         <v>19.100000000000001</v>
       </c>
       <c r="G9" s="2">
-        <f t="shared" si="0"/>
+        <f>+ROUNDUP(3/4*25.4*IF(B9="Articulada",12,18),-1)</f>
         <v>230</v>
       </c>
       <c r="H9" s="2">
@@ -1786,14 +1793,14 @@
         <v>19</v>
       </c>
       <c r="O9" t="str">
-        <f t="shared" si="1"/>
+        <f>+_xlfn.CONCAT(A9,"-",IF(B9="ARTICULADA","ART","EMP"),"-",C9)</f>
         <v>W8x31-ART-2°</v>
       </c>
       <c r="P9" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>26</v>
       </c>
@@ -1813,7 +1820,7 @@
         <v>19.100000000000001</v>
       </c>
       <c r="G10" s="2">
-        <f t="shared" si="0"/>
+        <f>+ROUNDUP(3/4*25.4*IF(B10="Articulada",12,18),-1)</f>
         <v>350</v>
       </c>
       <c r="H10" s="2">
@@ -1838,14 +1845,14 @@
         <v>17</v>
       </c>
       <c r="O10" t="str">
-        <f t="shared" si="1"/>
+        <f>+_xlfn.CONCAT(A10,"-",IF(B10="ARTICULADA","ART","EMP"),"-",C10)</f>
         <v>W8x31-EMP-1°</v>
       </c>
       <c r="P10" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>26</v>
       </c>
@@ -1865,7 +1872,7 @@
         <v>19.100000000000001</v>
       </c>
       <c r="G11" s="2">
-        <f t="shared" si="0"/>
+        <f>+ROUNDUP(3/4*25.4*IF(B11="Articulada",12,18),-1)</f>
         <v>350</v>
       </c>
       <c r="H11" s="2">
@@ -1890,14 +1897,14 @@
         <v>19</v>
       </c>
       <c r="O11" t="str">
-        <f t="shared" si="1"/>
+        <f>+_xlfn.CONCAT(A11,"-",IF(B11="ARTICULADA","ART","EMP"),"-",C11)</f>
         <v>W8x31-EMP-2°</v>
       </c>
       <c r="P11" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>27</v>
       </c>
@@ -1917,7 +1924,7 @@
         <v>25.4</v>
       </c>
       <c r="G12" s="2">
-        <f t="shared" ref="G12:G18" si="2">+ROUNDUP(25.4*IF(B12="Articulada",12,18),-1)</f>
+        <f>+ROUNDUP(25.4*IF(B12="Articulada",12,18),-1)</f>
         <v>310</v>
       </c>
       <c r="H12" s="3">
@@ -1942,14 +1949,14 @@
         <v>17</v>
       </c>
       <c r="O12" t="str">
-        <f t="shared" si="1"/>
+        <f>+_xlfn.CONCAT(A12,"-",IF(B12="ARTICULADA","ART","EMP"),"-",C12)</f>
         <v>W10x45-ART-1°</v>
       </c>
       <c r="P12" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>27</v>
       </c>
@@ -1969,7 +1976,7 @@
         <v>25.4</v>
       </c>
       <c r="G13" s="2">
-        <f t="shared" si="2"/>
+        <f>+ROUNDUP(25.4*IF(B13="Articulada",12,18),-1)</f>
         <v>460</v>
       </c>
       <c r="H13" s="3">
@@ -1994,14 +2001,14 @@
         <v>17</v>
       </c>
       <c r="O13" t="str">
-        <f t="shared" si="1"/>
+        <f>+_xlfn.CONCAT(A13,"-",IF(B13="ARTICULADA","ART","EMP"),"-",C13)</f>
         <v>W10x45-EMP-1°</v>
       </c>
       <c r="P13" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>27</v>
       </c>
@@ -2021,7 +2028,7 @@
         <v>25.4</v>
       </c>
       <c r="G14" s="2">
-        <f t="shared" si="2"/>
+        <f>+ROUNDUP(25.4*IF(B14="Articulada",12,18),-1)</f>
         <v>460</v>
       </c>
       <c r="H14" s="3">
@@ -2046,14 +2053,14 @@
         <v>29</v>
       </c>
       <c r="O14" t="str">
-        <f t="shared" si="1"/>
+        <f>+_xlfn.CONCAT(A14,"-",IF(B14="ARTICULADA","ART","EMP"),"-",C14)</f>
         <v>W10x45-EMP-2°</v>
       </c>
       <c r="P14" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>31</v>
       </c>
@@ -2073,7 +2080,7 @@
         <v>25.4</v>
       </c>
       <c r="G15" s="2">
-        <f t="shared" si="2"/>
+        <f>+ROUNDUP(25.4*IF(B15="Articulada",12,18),-1)</f>
         <v>310</v>
       </c>
       <c r="H15" s="2">
@@ -2086,7 +2093,7 @@
         <v>150</v>
       </c>
       <c r="K15" s="2">
-        <v>250</v>
+        <v>190</v>
       </c>
       <c r="L15" s="2">
         <v>150</v>
@@ -2098,12 +2105,14 @@
         <v>17</v>
       </c>
       <c r="O15" t="str">
-        <f t="shared" si="1"/>
+        <f>+_xlfn.CONCAT(A15,"-",IF(B15="ARTICULADA","ART","EMP"),"-",C15)</f>
         <v>W12x50-ART-1°</v>
       </c>
-      <c r="P15" s="5"/>
+      <c r="P15" s="5">
+        <v>1</v>
+      </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>31</v>
       </c>
@@ -2123,7 +2132,7 @@
         <v>25.4</v>
       </c>
       <c r="G16" s="2">
-        <f t="shared" si="2"/>
+        <f>+ROUNDUP(25.4*IF(B16="Articulada",12,18),-1)</f>
         <v>460</v>
       </c>
       <c r="H16" s="2">
@@ -2148,12 +2157,14 @@
         <v>17</v>
       </c>
       <c r="O16" t="str">
-        <f t="shared" si="1"/>
+        <f>+_xlfn.CONCAT(A16,"-",IF(B16="ARTICULADA","ART","EMP"),"-",C16)</f>
         <v>W12x50-EMP-1°</v>
       </c>
-      <c r="P16" s="5"/>
+      <c r="P16" s="5">
+        <v>1</v>
+      </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>32</v>
       </c>
@@ -2173,7 +2184,7 @@
         <v>25.4</v>
       </c>
       <c r="G17" s="2">
-        <f t="shared" si="2"/>
+        <f>+ROUNDUP(25.4*IF(B17="Articulada",12,18),-1)</f>
         <v>310</v>
       </c>
       <c r="H17" s="3">
@@ -2186,7 +2197,7 @@
         <v>200</v>
       </c>
       <c r="K17" s="3">
-        <v>280</v>
+        <v>220</v>
       </c>
       <c r="L17" s="2">
         <v>200</v>
@@ -2198,12 +2209,14 @@
         <v>17</v>
       </c>
       <c r="O17" t="str">
-        <f t="shared" si="1"/>
+        <f>+_xlfn.CONCAT(A17,"-",IF(B17="ARTICULADA","ART","EMP"),"-",C17)</f>
         <v>W14x74-ART-1°</v>
       </c>
-      <c r="P17" s="5"/>
+      <c r="P17" s="5">
+        <v>1</v>
+      </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>32</v>
       </c>
@@ -2223,7 +2236,7 @@
         <v>25.4</v>
       </c>
       <c r="G18" s="2">
-        <f t="shared" si="2"/>
+        <f>+ROUNDUP(25.4*IF(B18="Articulada",12,18),-1)</f>
         <v>460</v>
       </c>
       <c r="H18" s="3">
@@ -2239,7 +2252,7 @@
         <v>360</v>
       </c>
       <c r="L18" s="2">
-        <v>380</v>
+        <v>360</v>
       </c>
       <c r="M18" s="2" t="s">
         <v>16</v>
@@ -2248,23 +2261,25 @@
         <v>17</v>
       </c>
       <c r="O18" t="str">
-        <f t="shared" si="1"/>
+        <f>+_xlfn.CONCAT(A18,"-",IF(B18="ARTICULADA","ART","EMP"),"-",C18)</f>
         <v>W14x74-EMP-1°</v>
       </c>
-      <c r="P18" s="5"/>
+      <c r="P18" s="5">
+        <v>1</v>
+      </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>33</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>15</v>
@@ -2274,22 +2289,22 @@
       </c>
       <c r="G19" s="2">
         <f>+ROUNDUP(3/4*25.4*IF(B19="Articulada",12,18),-1)</f>
-        <v>230</v>
+        <v>350</v>
       </c>
       <c r="H19" s="2">
         <v>86</v>
       </c>
       <c r="I19" s="2">
-        <v>100</v>
+        <v>243</v>
       </c>
       <c r="J19" s="2">
-        <v>100</v>
+        <v>243</v>
       </c>
       <c r="K19" s="2">
-        <v>100</v>
+        <v>230</v>
       </c>
       <c r="L19" s="2">
-        <v>100</v>
+        <v>230</v>
       </c>
       <c r="M19" s="2" t="s">
         <v>16</v>
@@ -2298,12 +2313,14 @@
         <v>17</v>
       </c>
       <c r="O19" t="str">
-        <f t="shared" si="1"/>
-        <v>HEB160-ART-1°</v>
-      </c>
-      <c r="P19" s="5"/>
+        <f>+_xlfn.CONCAT(A19,"-",IF(B19="ARTICULADA","ART","EMP"),"-",C19)</f>
+        <v>HEB160-EMP-1°</v>
+      </c>
+      <c r="P19" s="5">
+        <v>1</v>
+      </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>33</v>
       </c>
@@ -2311,10 +2328,10 @@
         <v>20</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>15</v>
@@ -2330,116 +2347,120 @@
         <v>86</v>
       </c>
       <c r="I20" s="2">
-        <v>243</v>
+        <v>293</v>
       </c>
       <c r="J20" s="2">
-        <v>243</v>
+        <v>293</v>
       </c>
       <c r="K20" s="2">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="L20" s="2">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="M20" s="2" t="s">
         <v>16</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="O20" t="str">
-        <f t="shared" si="1"/>
-        <v>HEB160-EMP-1°</v>
-      </c>
-      <c r="P20" s="5"/>
+        <f>+_xlfn.CONCAT(A20,"-",IF(B20="ARTICULADA","ART","EMP"),"-",C20)</f>
+        <v>HEB160-EMP-2°</v>
+      </c>
+      <c r="P20" s="5">
+        <v>1</v>
+      </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>15</v>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>51</v>
       </c>
       <c r="F21" s="2">
         <v>19.100000000000001</v>
       </c>
       <c r="G21" s="2">
-        <f>+ROUNDUP(3/4*25.4*IF(B21="Articulada",12,18),-1)</f>
-        <v>350</v>
-      </c>
-      <c r="H21" s="2">
-        <v>86</v>
-      </c>
-      <c r="I21" s="2">
-        <v>293</v>
-      </c>
-      <c r="J21" s="2">
-        <v>293</v>
-      </c>
-      <c r="K21" s="2">
-        <v>300</v>
+        <f>+ROUNDUP(25.4*IF(B21="Articulada",12,18),-1)</f>
+        <v>310</v>
+      </c>
+      <c r="H21" s="3">
+        <v>90</v>
+      </c>
+      <c r="I21" s="3">
+        <v>150</v>
+      </c>
+      <c r="J21" s="3">
+        <v>150</v>
+      </c>
+      <c r="K21" s="3">
+        <v>150</v>
       </c>
       <c r="L21" s="2">
-        <v>300</v>
+        <v>80</v>
       </c>
       <c r="M21" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="N21" s="2" t="s">
-        <v>19</v>
+      <c r="N21" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="O21" t="str">
-        <f t="shared" si="1"/>
-        <v>HEB160-EMP-2°</v>
-      </c>
-      <c r="P21" s="5"/>
+        <f>+_xlfn.CONCAT(A21,"-",IF(B21="ARTICULADA","ART","EMP"),"-",C21)</f>
+        <v>HEB200-ART-1°</v>
+      </c>
+      <c r="P21" s="5">
+        <v>1</v>
+      </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>34</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F22" s="3">
-        <v>25.4</v>
+        <v>51</v>
+      </c>
+      <c r="F22" s="2">
+        <v>19.100000000000001</v>
       </c>
       <c r="G22" s="2">
         <f>+ROUNDUP(25.4*IF(B22="Articulada",12,18),-1)</f>
-        <v>310</v>
+        <v>460</v>
       </c>
       <c r="H22" s="3">
         <v>90</v>
       </c>
       <c r="I22" s="3">
-        <v>150</v>
+        <v>324</v>
       </c>
       <c r="J22" s="3">
-        <v>150</v>
+        <v>324</v>
       </c>
       <c r="K22" s="3">
-        <v>150</v>
+        <v>280</v>
       </c>
       <c r="L22" s="2">
-        <v>150</v>
+        <v>280</v>
       </c>
       <c r="M22" s="2" t="s">
         <v>16</v>
@@ -2448,12 +2469,14 @@
         <v>17</v>
       </c>
       <c r="O22" t="str">
-        <f t="shared" si="1"/>
-        <v>HEB200-ART-1°</v>
-      </c>
-      <c r="P22" s="5"/>
+        <f>+_xlfn.CONCAT(A22,"-",IF(B22="ARTICULADA","ART","EMP"),"-",C22)</f>
+        <v>HEB200-EMP-1°</v>
+      </c>
+      <c r="P22" s="5">
+        <v>1</v>
+      </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>34</v>
       </c>
@@ -2461,16 +2484,16 @@
         <v>20</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F23" s="3">
-        <v>25.4</v>
+        <v>51</v>
+      </c>
+      <c r="F23" s="2">
+        <v>19.100000000000001</v>
       </c>
       <c r="G23" s="2">
         <f>+ROUNDUP(25.4*IF(B23="Articulada",12,18),-1)</f>
@@ -2480,80 +2503,82 @@
         <v>90</v>
       </c>
       <c r="I23" s="3">
-        <v>324</v>
+        <v>374</v>
       </c>
       <c r="J23" s="3">
-        <v>324</v>
+        <v>374</v>
       </c>
       <c r="K23" s="3">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="L23" s="2">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="M23" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="N23" s="3" t="s">
-        <v>17</v>
+      <c r="N23" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="O23" t="str">
-        <f t="shared" si="1"/>
-        <v>HEB200-EMP-1°</v>
-      </c>
-      <c r="P23" s="5"/>
+        <f>+_xlfn.CONCAT(A23,"-",IF(B23="ARTICULADA","ART","EMP"),"-",C23)</f>
+        <v>HEB200-EMP-2°</v>
+      </c>
+      <c r="P23" s="5">
+        <v>1</v>
+      </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B24" s="3" t="s">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C24" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F24" s="3">
-        <v>25.4</v>
+      <c r="C24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F24" s="2">
+        <v>19.100000000000001</v>
       </c>
       <c r="G24" s="2">
-        <f>+ROUNDUP(25.4*IF(B24="Articulada",12,18),-1)</f>
-        <v>460</v>
-      </c>
-      <c r="H24" s="3">
-        <v>90</v>
-      </c>
-      <c r="I24" s="3">
-        <v>374</v>
-      </c>
-      <c r="J24" s="3">
-        <v>374</v>
-      </c>
-      <c r="K24" s="3">
-        <v>380</v>
+        <f>+ROUNDUP(3/4*25.4*IF(B24="Articulada",12,18),-1)</f>
+        <v>350</v>
+      </c>
+      <c r="H24" s="2">
+        <v>86</v>
+      </c>
+      <c r="I24" s="2">
+        <v>193</v>
+      </c>
+      <c r="J24" s="2">
+        <v>143</v>
+      </c>
+      <c r="K24" s="2">
+        <v>200</v>
       </c>
       <c r="L24" s="2">
-        <v>380</v>
+        <v>150</v>
       </c>
       <c r="M24" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="N24" s="3" t="s">
-        <v>29</v>
+      <c r="N24" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="O24" t="str">
-        <f t="shared" si="1"/>
-        <v>HEB200-EMP-2°</v>
+        <f>+_xlfn.CONCAT(A24,"-",IF(B24="ARTICULADA","ART","EMP"),"-",C24)</f>
+        <v>UPN140C-EMP-1°</v>
       </c>
       <c r="P24" s="5"/>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>43</v>
       </c>
@@ -2561,10 +2586,10 @@
         <v>20</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>15</v>
@@ -2580,62 +2605,62 @@
         <v>86</v>
       </c>
       <c r="I25" s="2">
+        <v>243</v>
+      </c>
+      <c r="J25" s="2">
         <v>193</v>
       </c>
-      <c r="J25" s="2">
-        <v>143</v>
-      </c>
       <c r="K25" s="2">
+        <v>250</v>
+      </c>
+      <c r="L25" s="2">
         <v>200</v>
-      </c>
-      <c r="L25" s="2">
-        <v>150</v>
       </c>
       <c r="M25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="O25" t="str">
-        <f t="shared" si="1"/>
-        <v>UPN140C-EMP-1°</v>
+        <f>+_xlfn.CONCAT(A25,"-",IF(B25="ARTICULADA","ART","EMP"),"-",C25)</f>
+        <v>UPN140C-EMP-2°</v>
       </c>
       <c r="P25" s="5"/>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B26" s="2" t="s">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A26" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B26" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C26" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D26" s="2" t="s">
+      <c r="C26" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D26" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="E26" s="2" t="s">
+      <c r="E26" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F26" s="2">
+      <c r="F26" s="3">
         <v>19.100000000000001</v>
       </c>
       <c r="G26" s="2">
         <f>+ROUNDUP(3/4*25.4*IF(B26="Articulada",12,18),-1)</f>
         <v>350</v>
       </c>
-      <c r="H26" s="2">
+      <c r="H26" s="3">
         <v>86</v>
       </c>
-      <c r="I26" s="2">
+      <c r="I26" s="3">
         <v>243</v>
       </c>
-      <c r="J26" s="2">
+      <c r="J26" s="3">
         <v>193</v>
       </c>
-      <c r="K26" s="2">
+      <c r="K26" s="3">
         <v>250</v>
       </c>
       <c r="L26" s="2">
@@ -2644,16 +2669,16 @@
       <c r="M26" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="N26" s="2" t="s">
-        <v>19</v>
+      <c r="N26" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="O26" t="str">
-        <f t="shared" si="1"/>
-        <v>UPN140C-EMP-2°</v>
+        <f>+_xlfn.CONCAT(A26,"-",IF(B26="ARTICULADA","ART","EMP"),"-",C26)</f>
+        <v>UPN180C-EMP-1°</v>
       </c>
       <c r="P26" s="5"/>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
         <v>44</v>
       </c>
@@ -2661,10 +2686,10 @@
         <v>20</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>15</v>
@@ -2680,80 +2705,80 @@
         <v>86</v>
       </c>
       <c r="I27" s="3">
+        <v>293</v>
+      </c>
+      <c r="J27" s="3">
         <v>243</v>
       </c>
-      <c r="J27" s="3">
-        <v>193</v>
-      </c>
       <c r="K27" s="3">
+        <v>300</v>
+      </c>
+      <c r="L27" s="2">
         <v>250</v>
-      </c>
-      <c r="L27" s="2">
-        <v>200</v>
       </c>
       <c r="M27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="N27" s="3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="O27" t="str">
-        <f t="shared" si="1"/>
-        <v>UPN180C-EMP-1°</v>
+        <f>+_xlfn.CONCAT(A27,"-",IF(B27="ARTICULADA","ART","EMP"),"-",C27)</f>
+        <v>UPN180C-EMP-2°</v>
       </c>
       <c r="P27" s="5"/>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B28" s="3" t="s">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B28" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C28" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F28" s="3">
-        <v>19.100000000000001</v>
+      <c r="C28" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F28" s="2">
+        <v>25.4</v>
       </c>
       <c r="G28" s="2">
-        <f>+ROUNDUP(3/4*25.4*IF(B28="Articulada",12,18),-1)</f>
-        <v>350</v>
+        <f>+ROUNDUP(25.4*IF(B28="Articulada",12,18),-1)</f>
+        <v>460</v>
       </c>
       <c r="H28" s="3">
-        <v>86</v>
-      </c>
-      <c r="I28" s="3">
-        <v>293</v>
-      </c>
-      <c r="J28" s="3">
-        <v>243</v>
-      </c>
-      <c r="K28" s="3">
-        <v>300</v>
+        <v>90</v>
+      </c>
+      <c r="I28" s="2">
+        <v>324</v>
+      </c>
+      <c r="J28" s="2">
+        <v>224</v>
+      </c>
+      <c r="K28" s="2">
+        <v>330</v>
       </c>
       <c r="L28" s="2">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="M28" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="N28" s="3" t="s">
-        <v>19</v>
+      <c r="N28" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="O28" t="str">
-        <f t="shared" si="1"/>
-        <v>UPN180C-EMP-2°</v>
+        <f>+_xlfn.CONCAT(A28,"-",IF(B28="ARTICULADA","ART","EMP"),"-",C28)</f>
+        <v>UPN220C-EMP-1°</v>
       </c>
       <c r="P28" s="5"/>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>45</v>
       </c>
@@ -2761,10 +2786,10 @@
         <v>20</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>28</v>
@@ -2780,84 +2805,35 @@
         <v>90</v>
       </c>
       <c r="I29" s="2">
-        <v>324</v>
+        <v>374</v>
       </c>
       <c r="J29" s="2">
-        <v>224</v>
+        <v>274</v>
       </c>
       <c r="K29" s="2">
-        <v>330</v>
+        <v>380</v>
       </c>
       <c r="L29" s="2">
-        <v>230</v>
+        <v>280</v>
       </c>
       <c r="M29" s="2" t="s">
         <v>16</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="O29" t="str">
-        <f t="shared" si="1"/>
-        <v>UPN220C-EMP-1°</v>
-      </c>
-      <c r="P29" s="5"/>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F30" s="2">
-        <v>25.4</v>
-      </c>
-      <c r="G30" s="2">
-        <f>+ROUNDUP(25.4*IF(B30="Articulada",12,18),-1)</f>
-        <v>460</v>
-      </c>
-      <c r="H30" s="3">
-        <v>90</v>
-      </c>
-      <c r="I30" s="2">
-        <v>374</v>
-      </c>
-      <c r="J30" s="2">
-        <v>274</v>
-      </c>
-      <c r="K30" s="2">
-        <v>380</v>
-      </c>
-      <c r="L30" s="2">
-        <v>280</v>
-      </c>
-      <c r="M30" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="N30" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="O30" t="str">
-        <f t="shared" si="1"/>
+        <f>+_xlfn.CONCAT(A29,"-",IF(B29="ARTICULADA","ART","EMP"),"-",C29)</f>
         <v>UPN220C-EMP-2°</v>
       </c>
-      <c r="P30" s="7"/>
+      <c r="P29" s="7"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>